--- a/school_surveys/009_school_quality_survey--school_surveys.xlsx
+++ b/school_surveys/009_school_quality_survey--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,7 +528,11 @@
           <t>Introduction</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please take a few minutes to answer these questions.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,12 +552,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>school_rating</t>
+          <t>School Rating</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>How would you rate your school?</t>
+          <t>Rate your school out of 3 (Good, Fair, Excellent)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -575,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>teachers_quality</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Teacher Quality</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe what you think about your teachers</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -598,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>facilities_satisfaction</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Facilities Satisfaction</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rate your satisfaction with the school facilities</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -621,10 +633,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>school_environment</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>School Environment</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Describe your experience in the school</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -634,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>communication_satisfaction</t>
+          <t>teacher_support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>communication_satisfaction</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Teacher Support</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Do you feel supported by your teachers?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -657,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>teacher_support</t>
+          <t>student_fellowship</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>teacher_support</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Student Interactions</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>How do you feel about student interactions?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -680,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>student_fellowship</t>
+          <t>student_satisfaction</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>student_fellowship</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Student Satisfaction</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Describe your satisfaction level with the school</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -703,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>student_satisfaction</t>
+          <t>teacher_quality_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>student_satisfaction</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Teacher Quality (2)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Describe what you think about your teachers</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -726,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>teacher_quality</t>
+          <t>facilities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>teacher_quality</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Are the facilities good?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -749,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>teacher_satisfaction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>facilities</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Teacher Satisfaction</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>How satisfied are you with your teacher?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -772,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>teacher_satisfaction</t>
+          <t>student_environment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>teacher_satisfaction</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Student Environment</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Describe your experience in the school environment</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -800,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>student_environment</t>
+          <t>teacher_communication</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>student_environment</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Teacher Communication</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Describe your experience with teacher communication</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -823,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>teacher_communication</t>
+          <t>parent_satisfaction</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>teacher_communication</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Parent Satisfaction</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Describe your parents' satisfaction</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -851,10 +903,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>class_size</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Class Size</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Describe your class size</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -869,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>parent_satisfaction</t>
+          <t>parent_quality</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>parent_satisfaction</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Parent Quality</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Describe what you think about your parents</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -887,20 +947,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>teacher_satisfaction</t>
+          <t>student_fellowship_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>teacher_satisfaction</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Student Fellowship 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>How do you feel about student interactions?</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -910,20 +974,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>student_rating</t>
+          <t>school_funding</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>student_rating</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>School Funding</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Is the school well funded?</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -938,15 +1006,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>school_funding</t>
+          <t>teacher_support_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>school_funding</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Teacher Support 2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Do you feel supported by your teachers?</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -956,20 +1028,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>teacher_support</t>
+          <t>parent_communication</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>teacher_support</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Parent Communication</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Describe your experience with parent communication</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
@@ -979,20 +1055,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>parent_quality</t>
+          <t>facilities_quality</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>parent_quality</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Facilities Quality</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Describe the quality of school facilities</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>no</t>
@@ -1002,90 +1082,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>parent_satisfaction</t>
+          <t>student_satisfaction_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>parent_satisfaction</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Student Satisfaction 2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Describe your satisfaction level with the school</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>teacher_satisfaction</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>teacher_satisfaction</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>teacher_communication</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>teacher_communication</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>facilities_quality</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>facilities_quality</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1164,17 +1179,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>teachers_quality_choices</t>
+          <t>school_rating_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1186,29 +1201,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>teacher_support_choices</t>
+          <t>teachers_quality_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1220,29 +1235,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>student_fellowship_choices</t>
+          <t>teacher_support_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1254,63 +1269,63 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>teacher_quality_choices</t>
+          <t>student_fellowship_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>teacher_quality_choices</t>
+          <t>teacher_quality_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>facilities_choices</t>
+          <t>teacher_quality_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1322,29 +1337,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>teacher_satisfaction_choices</t>
+          <t>facilities_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1356,97 +1371,97 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>parent_satisfaction_choices</t>
+          <t>teacher_satisfaction_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>parent_satisfaction_choices</t>
+          <t>parent_quality_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>teacher_satisfaction_choices</t>
+          <t>parent_quality_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>teacher_satisfaction_choices</t>
+          <t>student_fellowship_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>school_funding_choices</t>
+          <t>student_fellowship_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1458,148 +1473,63 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>teacher_support_choices</t>
+          <t>school_funding_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>teacher_support_choices</t>
+          <t>teacher_support_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>parent_quality_choices</t>
+          <t>teacher_support_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>parent_quality_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>parent_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>parent_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>dissatisfied</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>teacher_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>satisfied</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>teacher_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>dissatisfied</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Dissatisfied</t>
+          <t>False</t>
         </is>
       </c>
     </row>
